--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127776368</v>
+        <v>127770410</v>
       </c>
       <c r="B7" t="n">
-        <v>92037</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,32 +1248,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>757</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636568</v>
+        <v>636460</v>
       </c>
       <c r="R7" t="n">
-        <v>6555685</v>
+        <v>6555943</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,14 +1310,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>(Erastia aurantiaca)?</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127770410</v>
+        <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,27 +1360,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1374,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636460</v>
+        <v>636390</v>
       </c>
       <c r="R8" t="n">
-        <v>6555943</v>
+        <v>6556058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1670,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127771520</v>
+        <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>92037</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,46 +1700,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636390</v>
+        <v>636568</v>
       </c>
       <c r="R11" t="n">
-        <v>6556058</v>
+        <v>6555685</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,19 +1755,14 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>(Erastia aurantiaca)?</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,6 +1771,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,42 +1349,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127771520</v>
+        <v>127772403</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636390</v>
+        <v>636308</v>
       </c>
       <c r="R8" t="n">
-        <v>6556058</v>
+        <v>6556040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,38 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127772059</v>
+        <v>127771520</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>91358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636385</v>
+        <v>636390</v>
       </c>
       <c r="R9" t="n">
-        <v>6556057</v>
+        <v>6556058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B10" t="n">
-        <v>56855</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R10" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>127770410</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,38 +1349,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772403</v>
+        <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>91361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636308</v>
+        <v>636390</v>
       </c>
       <c r="R8" t="n">
-        <v>6556040</v>
+        <v>6556058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,42 +1465,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127771520</v>
+        <v>127772403</v>
       </c>
       <c r="B9" t="n">
-        <v>91358</v>
+        <v>56858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636390</v>
+        <v>636308</v>
       </c>
       <c r="R9" t="n">
-        <v>6556058</v>
+        <v>6556040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92043</v>
+        <v>92046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>127770410</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B9" t="n">
-        <v>56858</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,27 +1476,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R9" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772059</v>
+        <v>127772403</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636385</v>
+        <v>636308</v>
       </c>
       <c r="R10" t="n">
-        <v>6556057</v>
+        <v>6556040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92046</v>
+        <v>92054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127769403</v>
+        <v>127770952</v>
       </c>
       <c r="B4" t="n">
-        <v>91349</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636483</v>
+        <v>636412</v>
       </c>
       <c r="R4" t="n">
-        <v>6555838</v>
+        <v>6556017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127770952</v>
+        <v>127769403</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,43 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636412</v>
+        <v>636483</v>
       </c>
       <c r="R5" t="n">
-        <v>6556017</v>
+        <v>6555838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127772059</v>
+        <v>127772403</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,27 +1476,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636385</v>
+        <v>636308</v>
       </c>
       <c r="R9" t="n">
-        <v>6556057</v>
+        <v>6556040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R10" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92054</v>
+        <v>92055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127770952</v>
+        <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,43 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636412</v>
+        <v>636483</v>
       </c>
       <c r="R4" t="n">
-        <v>6556017</v>
+        <v>6555838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127769403</v>
+        <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,34 +1025,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636483</v>
+        <v>636412</v>
       </c>
       <c r="R5" t="n">
-        <v>6555838</v>
+        <v>6556017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95820</v>
+        <v>95821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,42 +1349,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127771520</v>
+        <v>127772059</v>
       </c>
       <c r="B8" t="n">
-        <v>91371</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636390</v>
+        <v>636385</v>
       </c>
       <c r="R8" t="n">
-        <v>6556058</v>
+        <v>6556057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,38 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127772403</v>
+        <v>127771520</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>91372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636308</v>
+        <v>636390</v>
       </c>
       <c r="R9" t="n">
-        <v>6556040</v>
+        <v>6556058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772059</v>
+        <v>127772403</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636385</v>
+        <v>636308</v>
       </c>
       <c r="R10" t="n">
-        <v>6556057</v>
+        <v>6556040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772059</v>
+        <v>127772403</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,27 +1360,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636385</v>
+        <v>636308</v>
       </c>
       <c r="R8" t="n">
-        <v>6556057</v>
+        <v>6556040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R10" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1349,38 +1349,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772403</v>
+        <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>91372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636308</v>
+        <v>636390</v>
       </c>
       <c r="R8" t="n">
-        <v>6556040</v>
+        <v>6556058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,42 +1465,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127771520</v>
+        <v>127772403</v>
       </c>
       <c r="B9" t="n">
-        <v>91372</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636390</v>
+        <v>636308</v>
       </c>
       <c r="R9" t="n">
-        <v>6556058</v>
+        <v>6556040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1349,42 +1349,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127771520</v>
+        <v>127772403</v>
       </c>
       <c r="B8" t="n">
-        <v>91372</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636390</v>
+        <v>636308</v>
       </c>
       <c r="R8" t="n">
-        <v>6556058</v>
+        <v>6556040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,38 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127772403</v>
+        <v>127771520</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>91372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636308</v>
+        <v>636390</v>
       </c>
       <c r="R9" t="n">
-        <v>6556040</v>
+        <v>6556058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,27 +1360,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R8" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772059</v>
+        <v>127772403</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636385</v>
+        <v>636308</v>
       </c>
       <c r="R10" t="n">
-        <v>6556057</v>
+        <v>6556040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>127769403</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127770952</v>
       </c>
       <c r="B5" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95822</v>
+        <v>95830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>127770410</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772059</v>
+        <v>127772403</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,27 +1360,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636385</v>
+        <v>636308</v>
       </c>
       <c r="R8" t="n">
-        <v>6556057</v>
+        <v>6556040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,42 +1461,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127771520</v>
+        <v>127772059</v>
       </c>
       <c r="B9" t="n">
-        <v>91372</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636390</v>
+        <v>636385</v>
       </c>
       <c r="R9" t="n">
-        <v>6556058</v>
+        <v>6556057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,38 +1573,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772403</v>
+        <v>127771520</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>91380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636308</v>
+        <v>636390</v>
       </c>
       <c r="R10" t="n">
-        <v>6556040</v>
+        <v>6556058</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92057</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127771738</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127771056</v>
       </c>
       <c r="B3" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127769403</v>
+        <v>127770952</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636483</v>
+        <v>636412</v>
       </c>
       <c r="R4" t="n">
-        <v>6555838</v>
+        <v>6556017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127770952</v>
+        <v>127769403</v>
       </c>
       <c r="B5" t="n">
-        <v>91380</v>
+        <v>91452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,43 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sarvsjön, Sarvsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636412</v>
+        <v>636483</v>
       </c>
       <c r="R5" t="n">
-        <v>6556017</v>
+        <v>6555838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
         <v>127772221</v>
       </c>
       <c r="B6" t="n">
-        <v>95830</v>
+        <v>95923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>127770410</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,27 +1360,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R8" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,38 +1461,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127772059</v>
+        <v>127771520</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>91472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1501,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636385</v>
+        <v>636390</v>
       </c>
       <c r="R9" t="n">
-        <v>6556057</v>
+        <v>6556058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,42 +1577,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127771520</v>
+        <v>127772403</v>
       </c>
       <c r="B10" t="n">
-        <v>91380</v>
+        <v>56876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636390</v>
+        <v>636308</v>
       </c>
       <c r="R10" t="n">
-        <v>6556058</v>
+        <v>6556040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
         <v>127776368</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92157</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1349,38 +1349,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127772059</v>
+        <v>127771520</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>91472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636385</v>
+        <v>636390</v>
       </c>
       <c r="R8" t="n">
-        <v>6556057</v>
+        <v>6556058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,42 +1465,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127771520</v>
+        <v>127772403</v>
       </c>
       <c r="B9" t="n">
-        <v>91472</v>
+        <v>56876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636390</v>
+        <v>636308</v>
       </c>
       <c r="R9" t="n">
-        <v>6556058</v>
+        <v>6556040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127772403</v>
+        <v>127772059</v>
       </c>
       <c r="B10" t="n">
-        <v>56876</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636308</v>
+        <v>636385</v>
       </c>
       <c r="R10" t="n">
-        <v>6556040</v>
+        <v>6556057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1788,6 +1788,228 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128739001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>636514</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6555798</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128741792</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>636512</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6555863</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,6 +2010,2057 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128748965</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92790</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>636535</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6555668</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128752787</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96080</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>636438</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6555839</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128751443</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>636377</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6556092</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128751247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>636376</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556075</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128750430</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>636437</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6555926</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128750666</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>636416</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6555978</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128752121</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>636293</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556072</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128751473</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>636379</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556093</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128749154</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>636526</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6555755</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128752315</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>636399</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6555993</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128751802</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>636371</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6556101</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128749572</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96033</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>210</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>636474</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6555818</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128751316</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>636354</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6556088</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128752241</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>636361</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6556002</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128750311</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>636437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6555920</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128750285</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>636444</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6555927</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128750515</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>636459</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6555994</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128751570</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>636386</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6556098</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128750785</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>636404</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6556045</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128752660</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92774</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>636434</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6555871</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128752462</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>636402</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6555975</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128748965</v>
+        <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>92790</v>
+        <v>96080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636535</v>
+        <v>636438</v>
       </c>
       <c r="R14" t="n">
-        <v>6555668</v>
+        <v>6555839</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128752787</v>
+        <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>96080</v>
+        <v>92790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636438</v>
+        <v>636535</v>
       </c>
       <c r="R15" t="n">
-        <v>6555839</v>
+        <v>6555668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128750666</v>
+        <v>128752121</v>
       </c>
       <c r="B19" t="n">
-        <v>92784</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636416</v>
+        <v>636293</v>
       </c>
       <c r="R19" t="n">
-        <v>6555978</v>
+        <v>6556072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128752121</v>
+        <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,21 +2605,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636293</v>
+        <v>636416</v>
       </c>
       <c r="R20" t="n">
-        <v>6556072</v>
+        <v>6555978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128752315</v>
+        <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>79708</v>
+        <v>92792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636399</v>
+        <v>636371</v>
       </c>
       <c r="R23" t="n">
-        <v>6555993</v>
+        <v>6556101</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128751802</v>
+        <v>128752315</v>
       </c>
       <c r="B24" t="n">
-        <v>92792</v>
+        <v>79708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636371</v>
+        <v>636399</v>
       </c>
       <c r="R24" t="n">
-        <v>6556101</v>
+        <v>6555993</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,32 +3093,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128749572</v>
+        <v>128751316</v>
       </c>
       <c r="B25" t="n">
-        <v>96033</v>
+        <v>79708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636474</v>
+        <v>636354</v>
       </c>
       <c r="R25" t="n">
-        <v>6555818</v>
+        <v>6556088</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3190,32 +3190,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128751316</v>
+        <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>79708</v>
+        <v>96033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>210</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636354</v>
+        <v>636474</v>
       </c>
       <c r="R26" t="n">
-        <v>6556088</v>
+        <v>6555818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96080</v>
+        <v>96081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128751247</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>128752121</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128752315</v>
       </c>
       <c r="B24" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128751316</v>
       </c>
       <c r="B25" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96034</v>
+        <v>96061</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91886</v>
+        <v>91913</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96108</v>
+        <v>96114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128751247</v>
       </c>
       <c r="B17" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>128752121</v>
       </c>
       <c r="B19" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128752315</v>
       </c>
       <c r="B24" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128751316</v>
       </c>
       <c r="B25" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96061</v>
+        <v>96067</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91913</v>
+        <v>91918</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96093</v>
+        <v>96098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128751247</v>
       </c>
       <c r="B17" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128752121</v>
       </c>
       <c r="B19" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128752315</v>
       </c>
       <c r="B24" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128751316</v>
       </c>
       <c r="B25" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96098</v>
+        <v>96101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91943</v>
+        <v>91946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128751247</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128752121</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128752315</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128751316</v>
       </c>
       <c r="B25" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96101</v>
+        <v>96111</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91946</v>
+        <v>91953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2025 artfynd.xlsx
+++ b/artfynd/A 39825-2025 artfynd.xlsx
@@ -1904,7 +1904,7 @@
         <v>128741792</v>
       </c>
       <c r="B13" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128752787</v>
       </c>
       <c r="B14" t="n">
-        <v>96158</v>
+        <v>96167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>128748965</v>
       </c>
       <c r="B15" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128751443</v>
       </c>
       <c r="B16" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128751247</v>
       </c>
       <c r="B17" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>128750430</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128752121</v>
       </c>
       <c r="B19" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>128750666</v>
       </c>
       <c r="B20" t="n">
-        <v>92855</v>
+        <v>92864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>128751473</v>
       </c>
       <c r="B21" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>128749154</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128751802</v>
       </c>
       <c r="B23" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128752315</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128751316</v>
       </c>
       <c r="B25" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128749572</v>
       </c>
       <c r="B26" t="n">
-        <v>96111</v>
+        <v>96120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128752241</v>
       </c>
       <c r="B27" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>128750311</v>
       </c>
       <c r="B28" t="n">
-        <v>92855</v>
+        <v>92864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128750285</v>
       </c>
       <c r="B29" t="n">
-        <v>92818</v>
+        <v>92827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128750515</v>
       </c>
       <c r="B30" t="n">
-        <v>92855</v>
+        <v>92864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>128751570</v>
       </c>
       <c r="B31" t="n">
-        <v>91497</v>
+        <v>91506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>128750785</v>
       </c>
       <c r="B32" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>128752660</v>
       </c>
       <c r="B33" t="n">
-        <v>92844</v>
+        <v>92853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>128752462</v>
       </c>
       <c r="B34" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
